--- a/data/trans_orig/P23_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130306</t>
+          <t>132268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171823</t>
+          <t>172301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77480</t>
+          <t>77273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107809</t>
+          <t>109460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219863</t>
+          <t>217758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>272366</t>
+          <t>269777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301953</t>
+          <t>301475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343470</t>
+          <t>341508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198871</t>
+          <t>197220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229200</t>
+          <t>229407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>508091</t>
+          <t>510680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560594</t>
+          <t>562699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116435</t>
+          <t>117186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153948</t>
+          <t>154573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114916</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>151665</t>
+          <t>153039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241458</t>
+          <t>237832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294779</t>
+          <t>293919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212986</t>
+          <t>212361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250499</t>
+          <t>249748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220200</t>
+          <t>218826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256949</t>
+          <t>256531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>444020</t>
+          <t>444880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>497341</t>
+          <t>500967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230814</t>
+          <t>231842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>278778</t>
+          <t>276686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58372</t>
+          <t>59070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274487</t>
+          <t>277163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>328587</t>
+          <t>327132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263611</t>
+          <t>265703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311575</t>
+          <t>310547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109410</t>
+          <t>108712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131326</t>
+          <t>132109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>381584</t>
+          <t>383039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>435684</t>
+          <t>433008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>526056</t>
+          <t>530297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>597482</t>
+          <t>599929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216307</t>
+          <t>214318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263940</t>
+          <t>265817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>762889</t>
+          <t>760972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>845078</t>
+          <t>848164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640852</t>
+          <t>638405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>712278</t>
+          <t>708037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450345</t>
+          <t>448468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497978</t>
+          <t>499967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1107542</t>
+          <t>1104456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1189731</t>
+          <t>1191648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167109</t>
+          <t>169808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205829</t>
+          <t>205795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159938</t>
+          <t>159204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204729</t>
+          <t>204183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337105</t>
+          <t>334898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>400243</t>
+          <t>399874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144726</t>
+          <t>144760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183446</t>
+          <t>180747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364023</t>
+          <t>364569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>408814</t>
+          <t>409548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>519064</t>
+          <t>519433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>582202</t>
+          <t>584409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73261</t>
+          <t>73717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103884</t>
+          <t>104418</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145347</t>
+          <t>147583</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194445</t>
+          <t>196095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>229320</t>
+          <t>230973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>285069</t>
+          <t>288110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193274</t>
+          <t>192740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223897</t>
+          <t>223441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1054315</t>
+          <t>1052665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1103413</t>
+          <t>1101177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1260849</t>
+          <t>1257808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1316598</t>
+          <t>1314945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1326109</t>
+          <t>1325402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1440110</t>
+          <t>1436148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>815977</t>
+          <t>808288</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>915986</t>
+          <t>909190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2170200</t>
+          <t>2166893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2325416</t>
+          <t>2328175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1829038</t>
+          <t>1833000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1943039</t>
+          <t>1943746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2462138</t>
+          <t>2468934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2562147</t>
+          <t>2569836</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4321856</t>
+          <t>4319097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4477072</t>
+          <t>4480379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126561</t>
+          <t>127651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169180</t>
+          <t>170909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>82105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117719</t>
+          <t>116990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221043</t>
+          <t>218912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276905</t>
+          <t>273430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268031</t>
+          <t>266302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310650</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196735</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231444</t>
+          <t>232349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474760</t>
+          <t>478235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530622</t>
+          <t>532753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131038</t>
+          <t>130915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174169</t>
+          <t>171150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108029</t>
+          <t>107609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146009</t>
+          <t>145238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>247796</t>
+          <t>249505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307115</t>
+          <t>306851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244628</t>
+          <t>247647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287759</t>
+          <t>287882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192002</t>
+          <t>192773</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229982</t>
+          <t>230402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449693</t>
+          <t>449957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509012</t>
+          <t>507303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248117</t>
+          <t>248544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>297885</t>
+          <t>300793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69933</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101367</t>
+          <t>100165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>328061</t>
+          <t>326080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>388525</t>
+          <t>387145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>331530</t>
+          <t>328622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381298</t>
+          <t>380871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>159964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>190196</t>
+          <t>189750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>501019</t>
+          <t>502399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561483</t>
+          <t>563464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>465106</t>
+          <t>460199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>533168</t>
+          <t>529579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257795</t>
+          <t>257062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>314648</t>
+          <t>313797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>735422</t>
+          <t>739610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>828576</t>
+          <t>830952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624812</t>
+          <t>628401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>692874</t>
+          <t>697781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451013</t>
+          <t>451864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507866</t>
+          <t>508599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1095065</t>
+          <t>1092689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1188219</t>
+          <t>1184031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>195300</t>
+          <t>195820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240875</t>
+          <t>241573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189483</t>
+          <t>192276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241649</t>
+          <t>243272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400481</t>
+          <t>400750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>467740</t>
+          <t>471736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269721</t>
+          <t>269023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>315296</t>
+          <t>314776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>518887</t>
+          <t>517264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>571053</t>
+          <t>568260</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>803392</t>
+          <t>799396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870651</t>
+          <t>870382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50607</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78375</t>
+          <t>77701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141592</t>
+          <t>141639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>187310</t>
+          <t>188574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>201820</t>
+          <t>202037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>255234</t>
+          <t>256299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188507</t>
+          <t>189181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216275</t>
+          <t>215687</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>922041</t>
+          <t>920777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>967759</t>
+          <t>967712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1120999</t>
+          <t>1119934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1174413</t>
+          <t>1174196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1294421</t>
+          <t>1296737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1415449</t>
+          <t>1415226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>920672</t>
+          <t>918013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1033500</t>
+          <t>1033139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2249069</t>
+          <t>2255438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2412621</t>
+          <t>2418628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2005431</t>
+          <t>2005654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2126459</t>
+          <t>2124143</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2514643</t>
+          <t>2515004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2627471</t>
+          <t>2630130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4556403</t>
+          <t>4550396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4719955</t>
+          <t>4713586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127762</t>
+          <t>128658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82960</t>
+          <t>82368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153156</t>
+          <t>151449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203112</t>
+          <t>199183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301330</t>
+          <t>300434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338462</t>
+          <t>338098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264095</t>
+          <t>264687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294574</t>
+          <t>293216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573035</t>
+          <t>576964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>622991</t>
+          <t>624698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89656</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124658</t>
+          <t>125591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83402</t>
+          <t>82401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119324</t>
+          <t>118369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180838</t>
+          <t>182241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232537</t>
+          <t>231757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>251497</t>
+          <t>250564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>286499</t>
+          <t>286320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251922</t>
+          <t>252877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287844</t>
+          <t>288845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>514864</t>
+          <t>515644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>566563</t>
+          <t>565160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193497</t>
+          <t>194585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241300</t>
+          <t>240601</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>66328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243660</t>
+          <t>243796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294742</t>
+          <t>297949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280614</t>
+          <t>281313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328417</t>
+          <t>327329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100854</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124716</t>
+          <t>125578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>393294</t>
+          <t>390087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444376</t>
+          <t>444240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405101</t>
+          <t>401767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>468402</t>
+          <t>472498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288381</t>
+          <t>288694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>343131</t>
+          <t>344372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711253</t>
+          <t>711055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>794935</t>
+          <t>797043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>680372</t>
+          <t>676276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>743673</t>
+          <t>747007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>480576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>536567</t>
+          <t>536254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1178787</t>
+          <t>1176679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1262469</t>
+          <t>1262667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>220029</t>
+          <t>218733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267940</t>
+          <t>268243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193723</t>
+          <t>192089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>244103</t>
+          <t>242825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427155</t>
+          <t>426787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>496108</t>
+          <t>494790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352766</t>
+          <t>352463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400677</t>
+          <t>401973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>493052</t>
+          <t>494330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>543432</t>
+          <t>545066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>861753</t>
+          <t>863071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>930706</t>
+          <t>931074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>58745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90578</t>
+          <t>89408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>151222</t>
+          <t>146901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200287</t>
+          <t>201066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>218778</t>
+          <t>218135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275611</t>
+          <t>277796</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196567</t>
+          <t>197737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226806</t>
+          <t>228400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>879343</t>
+          <t>878564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>928408</t>
+          <t>932729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1091164</t>
+          <t>1088979</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1147997</t>
+          <t>1148640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1134909</t>
+          <t>1128865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1243258</t>
+          <t>1248850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>876658</t>
+          <t>867898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>983412</t>
+          <t>975105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2021714</t>
+          <t>2029531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2190228</t>
+          <t>2185934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2140527</t>
+          <t>2134935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2248876</t>
+          <t>2254920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2542745</t>
+          <t>2551052</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2649499</t>
+          <t>2658259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4719715</t>
+          <t>4724009</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4888229</t>
+          <t>4880412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132268</t>
+          <t>133517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172301</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77273</t>
+          <t>77397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109460</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217758</t>
+          <t>218270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269777</t>
+          <t>269560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301475</t>
+          <t>300456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341508</t>
+          <t>340259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197220</t>
+          <t>197678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229407</t>
+          <t>229283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510680</t>
+          <t>510897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562699</t>
+          <t>562187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117186</t>
+          <t>117959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154573</t>
+          <t>153949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115334</t>
+          <t>115299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>153039</t>
+          <t>152157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>237832</t>
+          <t>241180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293919</t>
+          <t>294924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212361</t>
+          <t>212985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249748</t>
+          <t>248975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218826</t>
+          <t>219708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256531</t>
+          <t>256566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>444880</t>
+          <t>443875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500967</t>
+          <t>497619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>231842</t>
+          <t>231446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>276686</t>
+          <t>278602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59070</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277163</t>
+          <t>275964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>327132</t>
+          <t>330241</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265703</t>
+          <t>263787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310547</t>
+          <t>310943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108712</t>
+          <t>110746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132109</t>
+          <t>133124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>383039</t>
+          <t>379930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>433008</t>
+          <t>434207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>530297</t>
+          <t>528771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>599929</t>
+          <t>598253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214318</t>
+          <t>219801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>265817</t>
+          <t>268791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>760972</t>
+          <t>758777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>848164</t>
+          <t>849334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638405</t>
+          <t>640081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>708037</t>
+          <t>709563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448468</t>
+          <t>445494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499967</t>
+          <t>494484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1104456</t>
+          <t>1103286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191648</t>
+          <t>1193843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>169808</t>
+          <t>169681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205795</t>
+          <t>206815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159204</t>
+          <t>157432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204183</t>
+          <t>204324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>334898</t>
+          <t>337980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399874</t>
+          <t>398721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144760</t>
+          <t>143740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180747</t>
+          <t>180874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364569</t>
+          <t>364428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>409548</t>
+          <t>411320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>519433</t>
+          <t>520586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>584409</t>
+          <t>581327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73717</t>
+          <t>72990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104418</t>
+          <t>103067</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147583</t>
+          <t>147269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>196095</t>
+          <t>193175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>230973</t>
+          <t>229481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288110</t>
+          <t>289750</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192740</t>
+          <t>194091</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223441</t>
+          <t>224168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1052665</t>
+          <t>1055585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1101177</t>
+          <t>1101491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1257808</t>
+          <t>1256168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314945</t>
+          <t>1316437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1325402</t>
+          <t>1329459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1436148</t>
+          <t>1441411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>808288</t>
+          <t>811096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>909190</t>
+          <t>908837</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2166893</t>
+          <t>2167279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2328175</t>
+          <t>2317612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1833000</t>
+          <t>1827737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1943746</t>
+          <t>1939689</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2468934</t>
+          <t>2469287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2569836</t>
+          <t>2567028</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4319097</t>
+          <t>4329660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4480379</t>
+          <t>4479993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127651</t>
+          <t>128032</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170909</t>
+          <t>169187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82105</t>
+          <t>81774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116990</t>
+          <t>116931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218912</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273430</t>
+          <t>274258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266302</t>
+          <t>268024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309560</t>
+          <t>309179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>197523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232349</t>
+          <t>232680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478235</t>
+          <t>477407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532753</t>
+          <t>532911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130915</t>
+          <t>128634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171150</t>
+          <t>172067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107609</t>
+          <t>107213</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145238</t>
+          <t>144703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249505</t>
+          <t>247459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>306851</t>
+          <t>305074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247647</t>
+          <t>246730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287882</t>
+          <t>290163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192773</t>
+          <t>193308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230402</t>
+          <t>230798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449957</t>
+          <t>451734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>507303</t>
+          <t>509349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248544</t>
+          <t>247217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>300793</t>
+          <t>298124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>70904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100165</t>
+          <t>100584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>326080</t>
+          <t>328061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>387145</t>
+          <t>384303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328622</t>
+          <t>331291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380871</t>
+          <t>382198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159964</t>
+          <t>159545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189750</t>
+          <t>189225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>502399</t>
+          <t>505241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563464</t>
+          <t>561483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>460199</t>
+          <t>464671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>529579</t>
+          <t>533770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257062</t>
+          <t>258896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>313797</t>
+          <t>315083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>739610</t>
+          <t>735263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>830952</t>
+          <t>829099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628401</t>
+          <t>624210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>697781</t>
+          <t>693309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451864</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>508599</t>
+          <t>506765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1092689</t>
+          <t>1094542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1184031</t>
+          <t>1188378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>195820</t>
+          <t>196333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241573</t>
+          <t>241307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192276</t>
+          <t>188973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243272</t>
+          <t>243882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400750</t>
+          <t>400537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>471736</t>
+          <t>468434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269023</t>
+          <t>269289</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314776</t>
+          <t>314263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>517264</t>
+          <t>516654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>568260</t>
+          <t>571563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>799396</t>
+          <t>802698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870382</t>
+          <t>870595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51195</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77701</t>
+          <t>78623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141639</t>
+          <t>139909</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188574</t>
+          <t>188046</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202037</t>
+          <t>201169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>256299</t>
+          <t>255931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189181</t>
+          <t>188259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>215687</t>
+          <t>216665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>920777</t>
+          <t>921305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>967712</t>
+          <t>969442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1119934</t>
+          <t>1120302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1174196</t>
+          <t>1175064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1296737</t>
+          <t>1296920</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1415226</t>
+          <t>1414325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>918013</t>
+          <t>922732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1033139</t>
+          <t>1033789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2255438</t>
+          <t>2249195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2418628</t>
+          <t>2415869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2005654</t>
+          <t>2006555</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2124143</t>
+          <t>2123960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2515004</t>
+          <t>2514354</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2630130</t>
+          <t>2625411</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4550396</t>
+          <t>4553155</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4713586</t>
+          <t>4719829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90994</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128658</t>
+          <t>128289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82368</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151449</t>
+          <t>152174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199183</t>
+          <t>201149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300434</t>
+          <t>300803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338098</t>
+          <t>337922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264687</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293216</t>
+          <t>293509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>576964</t>
+          <t>574998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624698</t>
+          <t>623973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125591</t>
+          <t>126387</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82401</t>
+          <t>85114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>118682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>182241</t>
+          <t>182699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231757</t>
+          <t>233189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250564</t>
+          <t>249768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>286320</t>
+          <t>287775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252877</t>
+          <t>252564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288845</t>
+          <t>286132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>515644</t>
+          <t>514212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565160</t>
+          <t>564702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194585</t>
+          <t>195167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240601</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>65103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243796</t>
+          <t>242817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297949</t>
+          <t>295807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281313</t>
+          <t>280931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327329</t>
+          <t>326747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99795</t>
+          <t>101020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125578</t>
+          <t>124944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390087</t>
+          <t>392229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444240</t>
+          <t>445219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>401767</t>
+          <t>405052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>472498</t>
+          <t>471443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288694</t>
+          <t>289140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344372</t>
+          <t>343617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711055</t>
+          <t>711392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>797043</t>
+          <t>795160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676276</t>
+          <t>677331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>747007</t>
+          <t>743722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>480576</t>
+          <t>481331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>536254</t>
+          <t>535808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1176679</t>
+          <t>1178562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1262667</t>
+          <t>1262330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>218733</t>
+          <t>220640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268243</t>
+          <t>267811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192089</t>
+          <t>195244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242825</t>
+          <t>245294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426787</t>
+          <t>424969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>494790</t>
+          <t>494460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352463</t>
+          <t>352895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401973</t>
+          <t>400066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>494330</t>
+          <t>491861</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>545066</t>
+          <t>541911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>863071</t>
+          <t>863401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>931074</t>
+          <t>932892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58745</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89408</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>146901</t>
+          <t>150563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>201066</t>
+          <t>196675</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>218135</t>
+          <t>219162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>277796</t>
+          <t>275748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197737</t>
+          <t>199206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228400</t>
+          <t>229018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>878564</t>
+          <t>882955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>932729</t>
+          <t>929067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1088979</t>
+          <t>1091027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1148640</t>
+          <t>1147613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1128865</t>
+          <t>1125355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1248850</t>
+          <t>1237636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>867898</t>
+          <t>873874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>975105</t>
+          <t>980028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2029531</t>
+          <t>2038314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2185934</t>
+          <t>2194178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2134935</t>
+          <t>2146149</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2254920</t>
+          <t>2258430</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2551052</t>
+          <t>2546129</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2658259</t>
+          <t>2652283</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4724009</t>
+          <t>4715765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4880412</t>
+          <t>4871629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
